--- a/docs/homologacao/homologacao-importacao-FICTICIA.xlsx
+++ b/docs/homologacao/homologacao-importacao-FICTICIA.xlsx
@@ -2,8 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="LEIA-ME (ficticia)" sheetId="1" r:id="rId1"/>
-    <sheet name="Despesas" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -66,107 +65,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AVISO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PLANILHA FICTICIA - SOMENTE PARA HOMOLOGACAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Este arquivo NAO e, e nao representa, a exportacao real de despesas da AutEM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nenhum arquivo real de exportacao da AutEM foi recebido ate a data de geracao deste arquivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>As colunas reproduzem apenas a LISTA DE CAMPOS informada pelo Vitor, numa grafia plausivel,</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>para permitir construir e testar o importador antes de termos o arquivo verdadeiro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fornecedores, CNPJs, numeros de nota e valores sao inventados. Nenhum dado real da ASA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>aparece aqui, conforme a politica de dados ficticios do projeto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Quando o arquivo real chegar: comparar os cabecalhos com frontend/src/lib/importacao/mapeamento.ts,</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ajustar os apelidos aceitos, testar e validar com o Vitor.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
     <col min="12" max="12" width="21" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="16" max="16" width="21" customWidth="1"/>
     <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -182,7 +98,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Data de Lançamento</t>
+          <t>Lançamento</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -202,22 +118,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Número do Documento</t>
+          <t>Nº Documento</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Forma de Pagamento</t>
+          <t>Forma de Pgto.</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Cliente / Fornecedor</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Conta Bancária</t>
+          <t>Conta Bancaria</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -247,27 +163,40 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>Valor Pago (R$)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Valor Pago</t>
+          <t>Valor (R$)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Diferença (R$)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B2" s="2">
-        <v>46274</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46262</v>
-      </c>
-      <c r="D2" s="2">
-        <v>46266</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -281,65 +210,80 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>VM00111222</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Distribuidora Norte Pecas LTDA</t>
+          <t>Distribuidora Norte Pecas</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Banco do Brasil</t>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pecas de reposicao - lote 12</t>
+          <t>PECAS DE REPOSICAO</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Manutencao</t>
+          <t>MANUTENCAO FROTA</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Manutencao Geral</t>
+          <t>MANUTENCAO GERAL</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>linha completa e ja paga</t>
+          <t>linha liquidada
+valor pago igual ao valor</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Nao</t>
+          <t>01/01</t>
         </is>
       </c>
       <c r="P2">
-        <v>1500</v>
+        <v>-1500</v>
       </c>
       <c r="Q2">
-        <v>1500</v>
+        <v>-1500</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
-        <v>46280</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46266</v>
-      </c>
-      <c r="D3" s="2">
-        <v>46266</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -348,17 +292,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.333.444/0001-92</t>
+          <t>11.222.333/0001-81</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>NIC0333444</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -366,46 +310,66 @@
           <t>Auto Eletrica Bandeirante</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Revisao eletrica da frota</t>
+          <t>REVISAO ELETRICA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Manutencao</t>
+          <t>MANUTENCAO FROTA</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Manutencao Geral</t>
+          <t>MANUTENCAO GERAL</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>valor 1.500,50 como texto</t>
+          <t>em aberto - liquidacao vazia</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.500,50</t>
-        </is>
+          <t>01/01</t>
+        </is>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>-890.75</v>
+      </c>
+      <c r="R3">
+        <v>-89075</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
-        <v>46285</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46267</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46266</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -414,123 +378,169 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.444.555/0001-03</t>
+          <t>11.222.333/0001-81</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>AS01555666</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Pneus Cearense ME</t>
+          <t>Oficina Mecanica Vale Verde</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Recapagem de 4 pneus</t>
+          <t>RETIFICA DE MOTOR</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Manutencao</t>
+          <t>MANUTENCAO FROTA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Pneus</t>
+          <t>MANUTENCAO GERAL</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>valor 1.500 como texto (milhar)</t>
+          <t>parcela 8 de 12 - nao pode virar 1/1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
+          <t>08/12</t>
+        </is>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>-2400</v>
+      </c>
+      <c r="R4">
+        <v>-240000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
-        <v>46290</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46268</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46266</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Despesa</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11.222.333/0001-81</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AS01555666</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Servicos Gerais Aurora</t>
+          <t>Oficina Mecanica Vale Verde</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Limpeza do patio - setembro</t>
+          <t>RETIFICA DE MOTOR</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>MANUTENCAO FROTA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Servicos Terceirizados</t>
+          <t>MANUTENCAO GERAL</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>sem CNPJ e sem documento</t>
+          <t>parcela 9 de 12 - mesma nota, outro vencimento</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>09/12</t>
         </is>
       </c>
       <c r="P5">
-        <v>890.75</v>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>-2400</v>
+      </c>
+      <c r="R5">
+        <v>-240000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -540,62 +550,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.555.666/0001-14</t>
+          <t>11.222.333/0002-62</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>7788990</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>PIX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Papelaria Central EIRELI</t>
+          <t>Energia Litoral S.A.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PIX</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Material de escritorio</t>
+          <t>ENERGIA ELETRICA</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>DESPESA ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>ENERGIA ELETRICA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>datas em dd/mm/aaaa como texto</t>
+          <t>valor com centavos, pago por PIX</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Nao</t>
+          <t>08/12</t>
         </is>
       </c>
       <c r="P6">
-        <v>312.4</v>
+        <v>-4320.9</v>
+      </c>
+      <c r="Q6">
+        <v>-4320.9</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
-        <v>46305</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46270</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46266</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -604,62 +636,84 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>55.666.777/0001-25</t>
+          <t>11.222.333/0001-81</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>CARNE00123</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>CARNE</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Oficina Mecanica Vale Verde</t>
+          <t>Imobiliaria Ficticia ME</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Retifica de motor - parcela 1</t>
+          <t>ALUGUEL GALPAO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Manutencao</t>
+          <t>DESPESA ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Manutencao Geral</t>
+          <t>ALUGUEL</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>parcela 1 de 2 do mesmo documento</t>
+          <t>forma de pagamento sem correspondencia</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Nao</t>
+          <t>25/38</t>
         </is>
       </c>
       <c r="P7">
-        <v>2400</v>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>-6800</v>
+      </c>
+      <c r="R7">
+        <v>-680000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
-        <v>46336</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46270</v>
-      </c>
-      <c r="D8" s="2">
-        <v>46266</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -668,62 +722,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>55.666.777/0001-25</t>
+          <t>11.222.333/0001-81</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>MT00777001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Oficina Mecanica Vale Verde</t>
+          <t>Orgao de Transito Ficticio</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Retifica de motor - parcela 2</t>
+          <t>MULTA DE TRANSITO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Manutencao</t>
+          <t>IMPOSTOS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Manutencao Geral</t>
+          <t>MULTA DE TRANSITO</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>parcela 2 de 2 do mesmo documento</t>
+          <t>par ambiguo - documento diferente (1 de 2)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Nao</t>
+          <t>01/01</t>
         </is>
       </c>
       <c r="P8">
-        <v>2400</v>
+        <v>-104.13</v>
+      </c>
+      <c r="Q8">
+        <v>-104.13</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2">
-        <v>46295</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46271</v>
-      </c>
-      <c r="D9" s="2">
-        <v>46266</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -732,61 +808,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.777.888/0001-36</t>
+          <t>11.222.333/0001-81</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>MT00777002</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Transportes Rapido Sul</t>
+          <t>Orgao de Transito Ficticio</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Frete de pecas</t>
+          <t>MULTA DE TRANSITO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Logistica</t>
+          <t>IMPOSTOS</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>MULTA DE TRANSITO</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PROBLEMA: valor em branco</t>
+          <t>par ambiguo - documento diferente (2 de 2)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Nao</t>
-        </is>
+          <t>01/01</t>
+        </is>
+      </c>
+      <c r="P9">
+        <v>-104.13</v>
+      </c>
+      <c r="Q9">
+        <v>-104.13</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30/02/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="2">
-        <v>46272</v>
-      </c>
-      <c r="D10" s="2">
-        <v>46266</v>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -795,62 +894,87 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>77.888.999/0001-47</t>
+          <t>11.222.333/0001-81</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>NF00998877</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PIX</t>
+          <t>DEBITO AUTOMATICO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Lubrificantes do Nordeste</t>
+          <t>Servicos Gerais Aurora</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Oleo lubrificante - 200L</t>
+          <t>LIMPEZA DO PATIO</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Manutencao</t>
+          <t>DESPESA ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Lubrificantes</t>
+          <t>SERVICOS TERCEIRIZADOS</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>PROBLEMA: 30/02 nao existe</t>
+          <t>observacao longa
+segunda linha do texto
+terceira linha com mais detalhe
+quarta linha final</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Nao</t>
+          <t>06/12</t>
         </is>
       </c>
       <c r="P10">
-        <v>1180</v>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>-1180.4</v>
+      </c>
+      <c r="R10">
+        <v>-118040</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
-        <v>46300</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46273</v>
-      </c>
-      <c r="D11" s="2">
-        <v>46266</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -859,65 +983,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>88.999.000/0001-58</t>
+          <t>11.222.333/0001-81</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>AVULSO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Seguros Atlantico S.A.</t>
+          <t>Papelaria Central Ficticia</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Ajuste de apolice</t>
+          <t>MATERIAL DE ESCRITORIO</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>DESPESA ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Seguros</t>
+          <t>MATERIAL DE CONSUMO</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>PROBLEMA: valor zero</t>
+          <t>documento generico - fornecedor A</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Nao</t>
+          <t>01/01</t>
         </is>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
+      <c r="Q11">
+        <v>-312.4</v>
+      </c>
+      <c r="R11">
+        <v>-31240</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B12" s="2">
-        <v>46274</v>
-      </c>
-      <c r="C12" s="2">
-        <v>46262</v>
-      </c>
-      <c r="D12" s="2">
-        <v>46266</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -931,65 +1074,79 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>AVULSO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Distribuidora Norte Pecas LTDA</t>
+          <t>Pneus Cearense Ficticio</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Banco do Brasil</t>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Pecas de reposicao - lote 12</t>
+          <t>RECAPAGEM DE PNEUS</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Manutencao</t>
+          <t>MANUTENCAO FROTA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Manutencao Geral</t>
+          <t>PNEUS</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>repetida dentro do proprio arquivo</t>
+          <t>documento generico - fornecedor B (nao pode sumir)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Nao</t>
+          <t>01/01</t>
         </is>
       </c>
       <c r="P12">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>1500</v>
+        <v>-1875.5</v>
+      </c>
+      <c r="R12">
+        <v>-187550</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2">
-        <v>46310</v>
-      </c>
-      <c r="C13" s="2">
-        <v>46274</v>
-      </c>
-      <c r="D13" s="2">
-        <v>46266</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -998,46 +1155,142 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>99.000.111/0001-69</t>
+          <t>11.222.333/0001-81</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>NF00445566</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Debito automatico</t>
+          <t>BOLETO BANCARIO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Energia Litoral S.A.</t>
+          <t>Transportes Rapido Ficticio</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>FRETE DE PECAS</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>MANUTENCAO FROTA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Energia Eletrica</t>
+          <t>FRETES</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>sem descricao - usa o fornecedor</t>
+          <t>PROBLEMA: valor em branco</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>01/01</t>
         </is>
       </c>
       <c r="P13">
-        <v>4320.9</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30/02/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>11.222.333/0001-81</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NF00112233</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PIX</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Lubrificantes Ficticios</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CEF EMPRESA FICTICIA LTDA</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>OLEO LUBRIFICANTE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>MANUTENCAO FROTA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>LUBRIFICANTES</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>PROBLEMA: 30/02 nao existe</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>01/01</t>
+        </is>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>-1180</v>
+      </c>
+      <c r="R14">
+        <v>-118000</v>
       </c>
     </row>
   </sheetData>
